--- a/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
+++ b/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
+++ b/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,13 +634,13 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>20</v>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
+++ b/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,25 +634,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 159 active clubs district-wide.</t>
+          <t>Out of 158 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -728,10 +728,10 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>45</v>

--- a/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
+++ b/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,25 +634,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 158 active clubs district-wide.</t>
+          <t>Out of 159 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -728,10 +728,10 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>45</v>

--- a/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
+++ b/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="E7" s="6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,25 +634,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 159 active clubs district-wide.</t>
+          <t>Out of 158 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
+++ b/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
+++ b/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
+++ b/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
+++ b/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>2</v>
@@ -553,7 +553,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -637,22 +637,22 @@
         <v>25</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 158 active clubs district-wide.</t>
+          <t>Out of 157 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>

--- a/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
+++ b/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,25 +634,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 157 active clubs district-wide.</t>
+          <t>Out of 155 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
+++ b/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
+++ b/docs/exports/club/00698816_ICASL_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="E7" s="6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,25 +634,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>34</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 155 active clubs district-wide.</t>
+          <t>Out of 162 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>—</t>
         </is>
       </c>
     </row>
